--- a/r4-core-157-add-vbpk-as-patientidentifier/StructureDefinition-at-core-valueset.xlsx
+++ b/r4-core-157-add-vbpk-as-patientidentifier/StructureDefinition-at-core-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T10:22:16+00:00</t>
+    <t>2026-10-07T08:52:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
